--- a/grupos/1EM - Estadisticos 20211.xlsx
+++ b/grupos/1EM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="180">
   <si>
     <t>Materia</t>
   </si>
@@ -215,21 +215,21 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -242,25 +242,100 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
+  </si>
+  <si>
+    <t>ATZIRI</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>ADAL</t>
+  </si>
+  <si>
+    <t>YULIANA YAMILETT</t>
+  </si>
+  <si>
+    <t>ROSA ITZEL</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>CABRERA</t>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>CLEMENTE</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>DOLORES</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>JUAREZ</t>
@@ -269,24 +344,45 @@
     <t>JUSTO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
@@ -296,22 +392,25 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>GAMBINO</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>CID</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
   </si>
   <si>
     <t>MONTERO</t>
@@ -320,49 +419,79 @@
     <t>NEGRETE</t>
   </si>
   <si>
-    <t>PANZO</t>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>CERON</t>
   </si>
   <si>
     <t>VILLASEÑOR</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLOURENS</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>VENEGAS</t>
   </si>
   <si>
-    <t>NIETO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
-    <t>ESPINDOLA</t>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>ANDRES</t>
   </si>
   <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
     <t>RUTH</t>
   </si>
   <si>
-    <t>CARLOS EMILIO</t>
+    <t>AXEL EDUARDO</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
   </si>
   <si>
     <t>PERLA</t>
   </si>
   <si>
-    <t>ATZIRI</t>
-  </si>
-  <si>
     <t>EDNA</t>
   </si>
   <si>
     <t>AMISADAI</t>
   </si>
   <si>
-    <t>ZURISADAI</t>
+    <t>AMY JULIET</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>YULIET</t>
   </si>
   <si>
     <t>DARLA MARLENE</t>
@@ -371,27 +500,54 @@
     <t>MARIA MICHELLE</t>
   </si>
   <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>ADAL</t>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>SAIRA LEILANI</t>
   </si>
   <si>
     <t>MONICA AIME</t>
   </si>
   <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>ROSA JAZMIN</t>
+  </si>
+  <si>
+    <t>REBECA</t>
+  </si>
+  <si>
+    <t>BRIGITTE</t>
+  </si>
+  <si>
     <t>SAYURI BETSABE</t>
   </si>
   <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>GEMMA MARIA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
     <t>ANDRIK YOSIMAR</t>
   </si>
   <si>
-    <t>YULIANA YAMILETT</t>
-  </si>
-  <si>
     <t>IVANNA DANIELA</t>
   </si>
   <si>
@@ -399,162 +555,6 @@
   </si>
   <si>
     <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>REBECA</t>
-  </si>
-  <si>
-    <t>BRIGITTE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>GEMMA MARIA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>LIZETH</t>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -1064,19 +1064,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1100,10 +1100,10 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1123,16 +1123,16 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -1144,13 +1144,13 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1177,16 +1177,16 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1218,19 +1218,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1254,19 +1254,19 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1295,19 +1295,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1334,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1343,7 +1343,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1357,13 +1357,13 @@
         <v>-1</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -1375,16 +1375,16 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1411,13 +1411,13 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1449,19 +1449,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1488,16 +1488,16 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1511,16 +1511,16 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1529,13 +1529,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1565,16 +1565,16 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1585,10 +1585,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1603,19 +1603,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1639,10 +1639,10 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1665,7 +1665,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -1683,10 +1683,10 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1719,7 +1719,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1742,7 +1742,7 @@
         <v>-1</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1760,10 +1760,10 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1796,7 +1796,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1819,13 +1819,13 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -1834,16 +1834,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1873,13 +1873,13 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1911,19 +1911,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1950,16 +1950,16 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1988,16 +1988,16 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2027,7 +2027,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -2065,19 +2065,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2104,16 +2104,16 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2142,19 +2142,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2178,13 +2178,13 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2201,10 +2201,10 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -2222,13 +2222,13 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2255,13 +2255,13 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2290,25 +2290,25 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2335,7 +2335,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2344,7 +2344,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2367,7 +2367,7 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2376,13 +2376,13 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2412,7 +2412,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>-1</v>
@@ -2421,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2432,19 +2432,19 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>-1</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2453,16 +2453,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2486,19 +2486,19 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>-1</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2527,19 +2527,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2566,7 +2566,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2586,37 +2586,37 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2640,19 +2640,19 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>-1</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2681,19 +2681,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2720,10 +2720,10 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2746,7 +2746,7 @@
         <v>7</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>8</v>
@@ -2758,16 +2758,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2797,13 +2797,13 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2835,19 +2835,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2912,19 +2912,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2957,7 +2957,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2989,19 +2989,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3066,19 +3066,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3102,16 +3102,16 @@
         <v>9</v>
       </c>
       <c r="U30">
+        <v>9</v>
+      </c>
+      <c r="V30">
+        <v>8</v>
+      </c>
+      <c r="W30">
         <v>10</v>
       </c>
-      <c r="V30">
-        <v>6</v>
-      </c>
-      <c r="W30">
-        <v>9</v>
-      </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3143,19 +3143,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3188,7 +3188,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3220,19 +3220,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3256,19 +3256,19 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3297,19 +3297,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3336,16 +3336,16 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3374,19 +3374,19 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3413,16 +3413,16 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3436,7 +3436,7 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -3451,19 +3451,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3490,13 +3490,13 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3528,19 +3528,19 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3564,16 +3564,16 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>9</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3605,19 +3605,19 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3647,13 +3647,13 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3682,19 +3682,19 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3721,7 +3721,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3744,7 +3744,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -3753,25 +3753,25 @@
         <v>6</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3798,16 +3798,16 @@
         <v>6</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>6</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3836,19 +3836,19 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3875,7 +3875,7 @@
         <v>8</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W40">
         <v>10</v>
@@ -3895,28 +3895,28 @@
         <v>5</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E41">
         <v>-1</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H41">
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -3949,19 +3949,19 @@
         <v>5</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W41">
         <v>-1</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3972,7 +3972,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -3990,13 +3990,13 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L42">
         <v>-1</v>
@@ -4026,10 +4026,10 @@
         <v>6</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42">
         <v>9</v>
@@ -4049,7 +4049,7 @@
         <v>5</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D43">
         <v>7</v>
@@ -4067,19 +4067,19 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4103,7 +4103,7 @@
         <v>5</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V43">
         <v>7</v>
@@ -4129,10 +4129,10 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F44">
         <v>6</v>
@@ -4144,19 +4144,19 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4183,10 +4183,10 @@
         <v>7</v>
       </c>
       <c r="V44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>6</v>
@@ -4221,19 +4221,19 @@
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4257,10 +4257,10 @@
         <v>9</v>
       </c>
       <c r="U45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W45">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>6</v>
       </c>
       <c r="D46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>-1</v>
@@ -4301,16 +4301,16 @@
         <v>-1</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K46">
         <v>-1</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4337,13 +4337,13 @@
         <v>6</v>
       </c>
       <c r="V46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W46">
         <v>-1</v>
       </c>
       <c r="X46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y46">
         <v>6</v>
@@ -4411,30 +4411,30 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="G2">
+        <v>23.26</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>62.79</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.4</v>
-      </c>
-      <c r="I2">
-        <v>16</v>
-      </c>
-      <c r="J2">
-        <v>37.21</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4443,30 +4443,30 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>74.42</v>
+        <v>86.05</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>25.58</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4475,30 +4475,30 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>88.37</v>
+      </c>
+      <c r="G4">
+        <v>11.63</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.1</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>18.6</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4507,30 +4507,30 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>16.28</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4539,30 +4539,30 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>88.37</v>
+      </c>
+      <c r="G6">
+        <v>11.63</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>83.72</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.3</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>16.28</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -4571,19 +4571,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>88.37</v>
+        <v>97.67</v>
       </c>
       <c r="G7">
-        <v>11.63</v>
+        <v>2.33</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4599,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4628,39 +4628,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920289</v>
+        <v>21330051920294</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920289</v>
+        <v>21330051920296</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -4668,79 +4668,79 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920289</v>
+        <v>21330051920296</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920291</v>
+        <v>21330051920299</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920294</v>
+        <v>21330051920306</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920294</v>
+        <v>20330051920235</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
@@ -4748,862 +4748,62 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920294</v>
+        <v>21330051920309</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920295</v>
+        <v>21330051920325</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920295</v>
+        <v>21330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" t="s">
         <v>95</v>
       </c>
-      <c r="D10" t="s">
-        <v>110</v>
-      </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920296</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920296</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920296</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920296</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920296</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920297</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920297</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920298</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920299</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920299</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920304</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920304</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920305</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920306</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920306</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920235</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920235</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920235</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920235</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920235</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920309</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920309</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920309</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920309</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920309</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920311</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920319</v>
-      </c>
-      <c r="B37" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920324</v>
-      </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" t="s">
-        <v>122</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920324</v>
-      </c>
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920325</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920325</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920325</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" t="s">
-        <v>123</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920325</v>
-      </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920325</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920326</v>
-      </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>86</v>
-      </c>
-      <c r="D45" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920327</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920328</v>
-      </c>
-      <c r="B47" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920328</v>
-      </c>
-      <c r="B48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920330</v>
-      </c>
-      <c r="B49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920330</v>
-      </c>
-      <c r="B50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5642,254 +4842,254 @@
         <v>21330051920296</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920235</v>
+        <v>21330051920294</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
         <v>88</v>
       </c>
-      <c r="D3" t="s">
-        <v>118</v>
-      </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920309</v>
+        <v>21330051920299</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920325</v>
+        <v>21330051920306</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920289</v>
+        <v>20330051920235</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920294</v>
+        <v>21330051920309</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920295</v>
+        <v>21330051920325</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920297</v>
+        <v>21330051920330</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920299</v>
+        <v>21330051920289</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920304</v>
+        <v>21330051920290</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920306</v>
+        <v>21330051920291</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920324</v>
+        <v>21330051920292</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920328</v>
+        <v>21330051920293</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
         <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920330</v>
+        <v>21330051920295</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920291</v>
+        <v>21330051920297</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5897,112 +5097,112 @@
         <v>21330051920298</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920305</v>
+        <v>21330051920300</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920311</v>
+        <v>21330051920301</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920319</v>
+        <v>21330051920302</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920326</v>
+        <v>21330051920303</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920327</v>
+        <v>21330051920304</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920290</v>
+        <v>21330051920305</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
@@ -6013,13 +5213,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920292</v>
+        <v>21330051920307</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
         <v>160</v>
@@ -6030,13 +5230,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920293</v>
+        <v>21330051920308</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -6047,13 +5247,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920300</v>
+        <v>21330051920310</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -6064,13 +5264,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920301</v>
+        <v>21330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -6081,13 +5281,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920302</v>
+        <v>21330051920312</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -6098,13 +5298,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920303</v>
+        <v>21330051920313</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -6115,13 +5315,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920307</v>
+        <v>21330051920314</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
         <v>166</v>
@@ -6132,13 +5332,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920308</v>
+        <v>21330051920315</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -6149,16 +5349,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920310</v>
+        <v>21330051920316</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6166,16 +5366,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920312</v>
+        <v>21330051920317</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6183,16 +5383,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920313</v>
+        <v>21330051920318</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="D34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6200,16 +5400,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920314</v>
+        <v>21330051920319</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6217,16 +5417,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920315</v>
+        <v>21330051920320</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6234,16 +5434,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920316</v>
+        <v>21330051920321</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6251,13 +5451,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920317</v>
+        <v>21330051920322</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D38" t="s">
         <v>173</v>
@@ -6268,13 +5468,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920318</v>
+        <v>21330051920323</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
         <v>174</v>
@@ -6285,13 +5485,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920320</v>
+        <v>21330051920324</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D40" t="s">
         <v>175</v>
@@ -6302,13 +5502,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920321</v>
+        <v>21330051920326</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -6319,13 +5519,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920322</v>
+        <v>21330051920327</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
         <v>177</v>
@@ -6336,13 +5536,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s">
         <v>178</v>
@@ -6356,10 +5556,10 @@
         <v>21330051920329</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D44" t="s">
         <v>179</v>
@@ -6375,7 +5575,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6407,68 +5607,68 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920295</v>
+        <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920295</v>
+        <v>21330051920289</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920297</v>
+        <v>21330051920294</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6476,25 +5676,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920297</v>
+        <v>21330051920294</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -6502,19 +5702,19 @@
         <v>21330051920299</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6525,13 +5725,13 @@
         <v>21330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6540,24 +5740,24 @@
         <v>64</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920304</v>
+        <v>21330051920306</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>65</v>
@@ -6568,45 +5768,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920304</v>
+        <v>21330051920306</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920306</v>
+        <v>21330051920309</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -6614,39 +5814,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920306</v>
+        <v>21330051920309</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920324</v>
+        <v>21330051920330</v>
       </c>
       <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
         <v>87</v>
       </c>
-      <c r="C12" t="s">
-        <v>102</v>
-      </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -6655,27 +5855,27 @@
         <v>64</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920324</v>
+        <v>21330051920330</v>
       </c>
       <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
-        <v>102</v>
-      </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6683,22 +5883,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920327</v>
+        <v>21330051920297</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6706,39 +5906,39 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920327</v>
+        <v>21330051920298</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920328</v>
+        <v>21330051920304</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -6747,214 +5947,76 @@
         <v>64</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920328</v>
+        <v>21330051920324</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920330</v>
+        <v>21330051920327</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920330</v>
+        <v>21330051920328</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920291</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920298</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920305</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920311</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920319</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920326</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1EM - Estadisticos 20211.xlsx
+++ b/grupos/1EM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="180">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Morales Vallejo Jorge Luis</t>
@@ -1061,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -1138,7 +1138,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1215,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -1292,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -1328,7 +1328,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1369,7 +1369,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1405,7 +1405,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1446,7 +1446,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -1523,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1600,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1636,7 +1636,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1677,7 +1677,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1713,7 +1713,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1754,7 +1754,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1790,7 +1790,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1831,7 +1831,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -1908,7 +1908,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1944,7 +1944,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1985,7 +1985,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -2062,7 +2062,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -2139,7 +2139,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>8</v>
@@ -2216,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2252,7 +2252,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2293,7 +2293,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>9</v>
@@ -2370,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2447,7 +2447,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2524,7 +2524,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2560,7 +2560,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2601,7 +2601,7 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -2678,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -2755,7 +2755,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -2832,7 +2832,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>7</v>
@@ -2868,7 +2868,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2909,7 +2909,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>8</v>
@@ -2986,7 +2986,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>8</v>
@@ -3022,7 +3022,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -3063,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>8</v>
@@ -3140,7 +3140,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>7</v>
@@ -3176,7 +3176,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -3217,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -3294,7 +3294,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3371,7 +3371,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>8</v>
@@ -3407,7 +3407,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -3448,7 +3448,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3484,7 +3484,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3525,7 +3525,7 @@
         <v>8</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>9</v>
@@ -3602,7 +3602,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -3679,7 +3679,7 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
         <v>9</v>
@@ -3756,7 +3756,7 @@
         <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I39">
         <v>6</v>
@@ -3792,7 +3792,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>6</v>
@@ -3833,7 +3833,7 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>7</v>
@@ -3869,7 +3869,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>8</v>
@@ -3910,7 +3910,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -3987,7 +3987,7 @@
         <v>6</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I42">
         <v>6</v>
@@ -4023,7 +4023,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>6</v>
@@ -4064,7 +4064,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>7</v>
@@ -4141,7 +4141,7 @@
         <v>7</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I44">
         <v>7</v>
@@ -4218,7 +4218,7 @@
         <v>8</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I45">
         <v>8</v>
@@ -4254,7 +4254,7 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U45">
         <v>9</v>
@@ -4295,7 +4295,7 @@
         <v>6</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I46">
         <v>-1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4443,30 +4443,30 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G3">
+        <v>18.6</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>86.05</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>13.95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4475,25 +4475,25 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>88.37</v>
+        <v>86.05</v>
       </c>
       <c r="G4">
-        <v>11.63</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4663,7 +4663,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4723,7 +4723,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4743,7 +4743,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4763,7 +4763,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4783,7 +4783,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4803,7 +4803,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -5575,7 +5575,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5622,7 +5622,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5653,39 +5653,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920294</v>
+        <v>21330051920298</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920294</v>
+        <v>21330051920298</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5699,22 +5699,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920299</v>
+        <v>21330051920306</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920299</v>
+        <v>21330051920306</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5745,22 +5745,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920306</v>
+        <v>21330051920309</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5768,16 +5768,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920306</v>
+        <v>21330051920309</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5791,62 +5791,62 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920309</v>
+        <v>21330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920309</v>
+        <v>21330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920330</v>
+        <v>21330051920297</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5860,45 +5860,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920330</v>
+        <v>21330051920304</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920297</v>
+        <v>21330051920324</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5906,22 +5906,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920298</v>
+        <v>21330051920327</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5929,16 +5929,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920304</v>
+        <v>21330051920328</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -5947,75 +5947,6 @@
         <v>64</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920324</v>
-      </c>
-      <c r="B17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920327</v>
-      </c>
-      <c r="B18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920328</v>
-      </c>
-      <c r="B19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20211.xlsx
+++ b/grupos/1EM - Estadisticos 20211.xlsx
@@ -1612,7 +1612,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -2151,7 +2151,7 @@
         <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2690,7 +2690,7 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -3922,7 +3922,7 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3999,7 +3999,7 @@
         <v>9</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>

--- a/grupos/1EM - Estadisticos 20211.xlsx
+++ b/grupos/1EM - Estadisticos 20211.xlsx
@@ -1141,7 +1141,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>5</v>

--- a/grupos/1EM - Estadisticos 20211.xlsx
+++ b/grupos/1EM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="180">
   <si>
     <t>Materia</t>
   </si>
@@ -212,21 +212,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
@@ -242,322 +242,322 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>DOLORES</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>GIL</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>PANZO</t>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLOURENS</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
   </si>
   <si>
     <t>NIETO</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>AXEL EDUARDO</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
     <t>CARLOS EMILIO</t>
   </si>
   <si>
+    <t>PERLA</t>
+  </si>
+  <si>
     <t>ATZIRI</t>
   </si>
   <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
     <t>ZURISADAI</t>
   </si>
   <si>
+    <t>AMY JULIET</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>DARLA MARLENE</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
     <t>ANETTE JOCELYN</t>
   </si>
   <si>
     <t>JOSE RAFAEL</t>
   </si>
   <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
     <t>ADAL</t>
   </si>
   <si>
+    <t>SAIRA LEILANI</t>
+  </si>
+  <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>ROSA JAZMIN</t>
+  </si>
+  <si>
+    <t>REBECA</t>
+  </si>
+  <si>
+    <t>BRIGITTE</t>
+  </si>
+  <si>
+    <t>SAYURI BETSABE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>GEMMA MARIA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>ANDRIK YOSIMAR</t>
+  </si>
+  <si>
     <t>YULIANA YAMILETT</t>
   </si>
   <si>
+    <t>IVANNA DANIELA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>LIZETH</t>
+  </si>
+  <si>
     <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>REBECA</t>
-  </si>
-  <si>
-    <t>BRIGITTE</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>GEMMA MARIA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ANDRIK YOSIMAR</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>LIZETH</t>
   </si>
 </sst>
 </file>
@@ -1079,40 +1079,40 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1153,43 +1153,43 @@
         <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1233,37 +1233,37 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1310,22 +1310,22 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1334,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1354,7 +1354,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1372,7 +1372,7 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1387,34 +1387,34 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1464,22 +1464,22 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1488,16 +1488,16 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1508,13 +1508,13 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1526,49 +1526,49 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1618,40 +1618,40 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1680,7 +1680,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1689,46 +1689,46 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1739,7 +1739,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1757,7 +1757,7 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1766,46 +1766,46 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1846,28 +1846,28 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1879,10 +1879,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1926,40 +1926,40 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2000,37 +2000,37 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>7</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>8</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -2080,28 +2080,28 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2157,28 +2157,28 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -2219,7 +2219,7 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2231,25 +2231,25 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2261,13 +2261,13 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2311,22 +2311,22 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2335,13 +2335,13 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2361,7 +2361,7 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>6</v>
@@ -2373,49 +2373,49 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2438,7 +2438,7 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>6</v>
@@ -2456,7 +2456,7 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2465,40 +2465,40 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2533,7 +2533,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2542,25 +2542,25 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2569,7 +2569,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2592,7 +2592,7 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -2610,7 +2610,7 @@
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -2619,22 +2619,22 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2646,7 +2646,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2696,34 +2696,34 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>7</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2770,31 +2770,31 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>6</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2803,10 +2803,10 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2850,37 +2850,37 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>8</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2927,31 +2927,31 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -3004,34 +3004,34 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>7</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>6</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3081,22 +3081,22 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3111,10 +3111,10 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3158,22 +3158,22 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3185,7 +3185,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3235,22 +3235,22 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -3265,10 +3265,10 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3312,22 +3312,22 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3339,7 +3339,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3389,22 +3389,22 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3422,7 +3422,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3466,22 +3466,22 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3490,7 +3490,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3543,22 +3543,22 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3576,7 +3576,7 @@
         <v>8</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3620,40 +3620,40 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>8</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>8</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3697,22 +3697,22 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3721,7 +3721,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3774,25 +3774,25 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>6</v>
@@ -3807,7 +3807,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3851,22 +3851,22 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>8</v>
@@ -3875,10 +3875,10 @@
         <v>8</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>8</v>
@@ -3901,7 +3901,7 @@
         <v>5</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F41">
         <v>5</v>
@@ -3919,31 +3919,31 @@
         <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>5</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
         <v>5</v>
@@ -3955,7 +3955,7 @@
         <v>5</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X41">
         <v>5</v>
@@ -4002,25 +4002,25 @@
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T42">
         <v>7</v>
@@ -4082,34 +4082,34 @@
         <v>6</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V43">
         <v>7</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -4159,22 +4159,22 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
         <v>6</v>
@@ -4183,16 +4183,16 @@
         <v>7</v>
       </c>
       <c r="V44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X44">
         <v>6</v>
       </c>
       <c r="Y44">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4236,37 +4236,37 @@
         <v>8</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V45">
         <v>9</v>
       </c>
       <c r="W45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y45">
         <v>8</v>
@@ -4286,7 +4286,7 @@
         <v>5</v>
       </c>
       <c r="E46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F46">
         <v>6</v>
@@ -4298,13 +4298,13 @@
         <v>6</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J46">
         <v>5</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L46">
         <v>7</v>
@@ -4313,40 +4313,40 @@
         <v>6</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V46">
         <v>5</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y46">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -4411,19 +4411,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>76.73999999999999</v>
+        <v>74.42</v>
       </c>
       <c r="G2">
-        <v>23.26</v>
+        <v>25.58</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4443,19 +4443,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>81.40000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G3">
-        <v>18.6</v>
+        <v>20.93</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4475,30 +4475,30 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>86.05</v>
+        <v>83.72</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>16.28</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4507,30 +4507,30 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>88.37</v>
+        <v>86.05</v>
       </c>
       <c r="G5">
-        <v>4.65</v>
+        <v>13.95</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4539,19 +4539,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>88.37</v>
+        <v>90.7</v>
       </c>
       <c r="G6">
-        <v>11.63</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4571,19 +4571,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>97.67</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="G7">
-        <v>2.33</v>
+        <v>4.65</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4599,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4624,186 +4624,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920294</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920296</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920296</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920299</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920306</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920235</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920309</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920325</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920330</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4839,149 +4659,149 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920296</v>
+        <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920294</v>
+        <v>21330051920290</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920299</v>
+        <v>21330051920291</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920306</v>
+        <v>21330051920292</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920235</v>
+        <v>21330051920293</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920309</v>
+        <v>21330051920294</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920325</v>
+        <v>21330051920295</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920330</v>
+        <v>21330051920296</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920289</v>
+        <v>21330051920297</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
         <v>146</v>
@@ -4992,13 +4812,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920290</v>
+        <v>21330051920298</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
         <v>147</v>
@@ -5009,13 +4829,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920291</v>
+        <v>21330051920299</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -5026,13 +4846,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920292</v>
+        <v>21330051920300</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
         <v>149</v>
@@ -5043,13 +4863,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920293</v>
+        <v>21330051920301</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
         <v>150</v>
@@ -5060,13 +4880,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920295</v>
+        <v>21330051920302</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
         <v>151</v>
@@ -5077,13 +4897,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920297</v>
+        <v>21330051920303</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
         <v>152</v>
@@ -5094,13 +4914,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920298</v>
+        <v>21330051920304</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
         <v>153</v>
@@ -5111,13 +4931,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920300</v>
+        <v>21330051920305</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
         <v>154</v>
@@ -5128,13 +4948,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920301</v>
+        <v>21330051920306</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
         <v>155</v>
@@ -5145,13 +4965,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920302</v>
+        <v>20330051920235</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
         <v>156</v>
@@ -5162,13 +4982,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920303</v>
+        <v>21330051920307</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>157</v>
@@ -5179,13 +4999,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920304</v>
+        <v>21330051920308</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>158</v>
@@ -5196,13 +5016,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920305</v>
+        <v>21330051920309</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
@@ -5213,13 +5033,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920307</v>
+        <v>21330051920310</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
         <v>160</v>
@@ -5230,13 +5050,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920308</v>
+        <v>21330051920311</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -5247,13 +5067,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920310</v>
+        <v>21330051920312</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -5264,13 +5084,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920311</v>
+        <v>21330051920313</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -5281,13 +5101,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920312</v>
+        <v>21330051920314</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -5298,13 +5118,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920313</v>
+        <v>21330051920315</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -5315,16 +5135,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920314</v>
+        <v>21330051920316</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5332,16 +5152,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920315</v>
+        <v>21330051920317</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5349,16 +5169,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920316</v>
+        <v>21330051920318</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5366,13 +5186,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920317</v>
+        <v>21330051920319</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
         <v>168</v>
@@ -5383,13 +5203,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920318</v>
+        <v>21330051920320</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
         <v>169</v>
@@ -5400,13 +5220,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920319</v>
+        <v>21330051920321</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
         <v>170</v>
@@ -5417,13 +5237,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920320</v>
+        <v>21330051920322</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
         <v>171</v>
@@ -5434,13 +5254,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920321</v>
+        <v>21330051920323</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
         <v>172</v>
@@ -5451,13 +5271,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920322</v>
+        <v>21330051920324</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
         <v>173</v>
@@ -5468,13 +5288,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920323</v>
+        <v>21330051920325</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
         <v>174</v>
@@ -5485,13 +5305,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920324</v>
+        <v>21330051920326</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
         <v>175</v>
@@ -5502,13 +5322,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920326</v>
+        <v>21330051920327</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -5519,13 +5339,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920327</v>
+        <v>21330051920328</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="D42" t="s">
         <v>177</v>
@@ -5536,13 +5356,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920328</v>
+        <v>21330051920329</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
         <v>178</v>
@@ -5553,13 +5373,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>21330051920329</v>
+        <v>21330051920330</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
         <v>179</v>
@@ -5575,7 +5395,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5610,19 +5430,19 @@
         <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5633,19 +5453,19 @@
         <v>21330051920289</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5653,22 +5473,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920298</v>
+        <v>21330051920294</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5676,22 +5496,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920298</v>
+        <v>21330051920294</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5699,45 +5519,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920306</v>
+        <v>21330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920306</v>
+        <v>21330051920297</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5745,45 +5565,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920309</v>
+        <v>21330051920304</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920309</v>
+        <v>21330051920304</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5791,22 +5611,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920330</v>
+        <v>21330051920309</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5814,139 +5634,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920330</v>
+        <v>21330051920309</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920297</v>
+        <v>21330051920295</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920304</v>
-      </c>
-      <c r="B13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920324</v>
-      </c>
-      <c r="B14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920327</v>
-      </c>
-      <c r="B15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920328</v>
-      </c>
-      <c r="B16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>
